--- a/data/Datasety-1_cleaned.xlsx
+++ b/data/Datasety-1_cleaned.xlsx
@@ -5,22 +5,34 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/an.kornn/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/an.kornn/PycharmProjects/Diplom_Depart/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{692661AB-5B74-904E-8563-905371A41E37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A61FF3E-68CD-7E48-8D5D-1AF77E2E0792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="15660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="626">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="673" uniqueCount="649">
   <si>
     <t>Год</t>
   </si>
@@ -1696,9 +1708,6 @@
     <t>2023</t>
   </si>
   <si>
-    <t>356719.9</t>
-  </si>
-  <si>
     <t>15946597.2</t>
   </si>
   <si>
@@ -1898,6 +1907,78 @@
   </si>
   <si>
     <t>318288.68</t>
+  </si>
+  <si>
+    <t>ИФО, %</t>
+  </si>
+  <si>
+    <t>107.8</t>
+  </si>
+  <si>
+    <t>86.1</t>
+  </si>
+  <si>
+    <t>116.9</t>
+  </si>
+  <si>
+    <t>127.2</t>
+  </si>
+  <si>
+    <t>102.3</t>
+  </si>
+  <si>
+    <t>157.2</t>
+  </si>
+  <si>
+    <t>136.6</t>
+  </si>
+  <si>
+    <t>138.6</t>
+  </si>
+  <si>
+    <t>108.6</t>
+  </si>
+  <si>
+    <t>96.8</t>
+  </si>
+  <si>
+    <t>112.4</t>
+  </si>
+  <si>
+    <t>103.2</t>
+  </si>
+  <si>
+    <t>117.9</t>
+  </si>
+  <si>
+    <t>95.1</t>
+  </si>
+  <si>
+    <t>78.9</t>
+  </si>
+  <si>
+    <t>105.0</t>
+  </si>
+  <si>
+    <t>112.8</t>
+  </si>
+  <si>
+    <t>80.3</t>
+  </si>
+  <si>
+    <t>93.2</t>
+  </si>
+  <si>
+    <t>75.0</t>
+  </si>
+  <si>
+    <t>132.2</t>
+  </si>
+  <si>
+    <t>85.0</t>
+  </si>
+  <si>
+    <t>329515.2</t>
   </si>
 </sst>
 </file>
@@ -1927,7 +2008,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1950,13 +2031,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -2261,13 +2356,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z27"/>
+  <dimension ref="A1:AA27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="5" max="5" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2346,13 +2441,16 @@
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="AA1" s="2" t="s">
+        <v>625</v>
+      </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>26</v>
       </c>
       <c r="B2" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C2" t="s">
         <v>27</v>
@@ -2361,7 +2459,7 @@
         <v>28</v>
       </c>
       <c r="E2" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="F2" t="s">
         <v>29</v>
@@ -2426,13 +2524,16 @@
       <c r="Z2" t="s">
         <v>47</v>
       </c>
+      <c r="AA2" t="s">
+        <v>626</v>
+      </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>48</v>
       </c>
       <c r="B3" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C3" t="s">
         <v>49</v>
@@ -2506,13 +2607,16 @@
       <c r="Z3" t="s">
         <v>69</v>
       </c>
+      <c r="AA3" t="s">
+        <v>627</v>
+      </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>70</v>
       </c>
       <c r="B4" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C4" t="s">
         <v>71</v>
@@ -2521,7 +2625,7 @@
         <v>72</v>
       </c>
       <c r="E4" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="F4" t="s">
         <v>73</v>
@@ -2586,13 +2690,16 @@
       <c r="Z4" t="s">
         <v>91</v>
       </c>
+      <c r="AA4" t="s">
+        <v>628</v>
+      </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>92</v>
       </c>
       <c r="B5" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C5" t="s">
         <v>93</v>
@@ -2666,13 +2773,16 @@
       <c r="Z5" t="s">
         <v>113</v>
       </c>
+      <c r="AA5" t="s">
+        <v>629</v>
+      </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>114</v>
       </c>
       <c r="B6" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C6" t="s">
         <v>115</v>
@@ -2681,7 +2791,7 @@
         <v>116</v>
       </c>
       <c r="E6" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="F6" t="s">
         <v>117</v>
@@ -2746,13 +2856,16 @@
       <c r="Z6" t="s">
         <v>135</v>
       </c>
+      <c r="AA6" t="s">
+        <v>626</v>
+      </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>136</v>
       </c>
       <c r="B7" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C7" t="s">
         <v>137</v>
@@ -2761,7 +2874,7 @@
         <v>138</v>
       </c>
       <c r="E7" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="F7" t="s">
         <v>139</v>
@@ -2826,13 +2939,16 @@
       <c r="Z7" t="s">
         <v>157</v>
       </c>
+      <c r="AA7" t="s">
+        <v>630</v>
+      </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>158</v>
       </c>
       <c r="B8" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C8" t="s">
         <v>159</v>
@@ -2841,7 +2957,7 @@
         <v>160</v>
       </c>
       <c r="E8" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="F8" t="s">
         <v>161</v>
@@ -2906,13 +3022,16 @@
       <c r="Z8" t="s">
         <v>179</v>
       </c>
+      <c r="AA8" t="s">
+        <v>631</v>
+      </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>180</v>
       </c>
       <c r="B9" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C9" t="s">
         <v>181</v>
@@ -2921,7 +3040,7 @@
         <v>182</v>
       </c>
       <c r="E9" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="F9" t="s">
         <v>183</v>
@@ -2986,13 +3105,16 @@
       <c r="Z9" t="s">
         <v>201</v>
       </c>
+      <c r="AA9" t="s">
+        <v>632</v>
+      </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>202</v>
       </c>
       <c r="B10" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C10" t="s">
         <v>203</v>
@@ -3001,7 +3123,7 @@
         <v>204</v>
       </c>
       <c r="E10" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="F10" t="s">
         <v>205</v>
@@ -3066,13 +3188,16 @@
       <c r="Z10" t="s">
         <v>221</v>
       </c>
+      <c r="AA10" t="s">
+        <v>633</v>
+      </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>222</v>
       </c>
       <c r="B11" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C11" t="s">
         <v>223</v>
@@ -3081,7 +3206,7 @@
         <v>224</v>
       </c>
       <c r="E11" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="F11" t="s">
         <v>225</v>
@@ -3146,13 +3271,16 @@
       <c r="Z11" t="s">
         <v>242</v>
       </c>
+      <c r="AA11" t="s">
+        <v>634</v>
+      </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>243</v>
       </c>
       <c r="B12" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C12" t="s">
         <v>244</v>
@@ -3161,7 +3289,7 @@
         <v>245</v>
       </c>
       <c r="E12" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="F12" t="s">
         <v>246</v>
@@ -3226,13 +3354,16 @@
       <c r="Z12" t="s">
         <v>264</v>
       </c>
+      <c r="AA12" t="s">
+        <v>226</v>
+      </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>265</v>
       </c>
       <c r="B13" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C13" t="s">
         <v>266</v>
@@ -3241,7 +3372,7 @@
         <v>267</v>
       </c>
       <c r="E13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="F13" t="s">
         <v>268</v>
@@ -3306,13 +3437,16 @@
       <c r="Z13" t="s">
         <v>286</v>
       </c>
+      <c r="AA13" t="s">
+        <v>635</v>
+      </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>287</v>
       </c>
       <c r="B14" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C14" t="s">
         <v>288</v>
@@ -3386,13 +3520,16 @@
       <c r="Z14" t="s">
         <v>307</v>
       </c>
+      <c r="AA14" t="s">
+        <v>211</v>
+      </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>308</v>
       </c>
       <c r="B15" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C15" t="s">
         <v>309</v>
@@ -3401,7 +3538,7 @@
         <v>310</v>
       </c>
       <c r="E15" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="F15" t="s">
         <v>311</v>
@@ -3466,13 +3603,16 @@
       <c r="Z15" t="s">
         <v>327</v>
       </c>
+      <c r="AA15" t="s">
+        <v>636</v>
+      </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>328</v>
       </c>
       <c r="B16" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C16" t="s">
         <v>329</v>
@@ -3481,7 +3621,7 @@
         <v>330</v>
       </c>
       <c r="E16" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="F16" t="s">
         <v>331</v>
@@ -3546,13 +3686,16 @@
       <c r="Z16" t="s">
         <v>349</v>
       </c>
+      <c r="AA16" t="s">
+        <v>637</v>
+      </c>
     </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>350</v>
       </c>
       <c r="B17" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C17" t="s">
         <v>351</v>
@@ -3561,7 +3704,7 @@
         <v>352</v>
       </c>
       <c r="E17" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="F17" t="s">
         <v>353</v>
@@ -3626,13 +3769,16 @@
       <c r="Z17" t="s">
         <v>370</v>
       </c>
+      <c r="AA17" t="s">
+        <v>638</v>
+      </c>
     </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>371</v>
       </c>
       <c r="B18" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C18" t="s">
         <v>372</v>
@@ -3641,7 +3787,7 @@
         <v>373</v>
       </c>
       <c r="E18" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="F18" t="s">
         <v>374</v>
@@ -3706,13 +3852,16 @@
       <c r="Z18" t="s">
         <v>392</v>
       </c>
+      <c r="AA18" t="s">
+        <v>639</v>
+      </c>
     </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>393</v>
       </c>
       <c r="B19" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C19" t="s">
         <v>394</v>
@@ -3721,7 +3870,7 @@
         <v>395</v>
       </c>
       <c r="E19" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="F19" t="s">
         <v>396</v>
@@ -3786,8 +3935,11 @@
       <c r="Z19" t="s">
         <v>413</v>
       </c>
+      <c r="AA19" t="s">
+        <v>640</v>
+      </c>
     </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>414</v>
       </c>
@@ -3801,7 +3953,7 @@
         <v>417</v>
       </c>
       <c r="E20" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="F20" t="s">
         <v>418</v>
@@ -3866,8 +4018,11 @@
       <c r="Z20" t="s">
         <v>434</v>
       </c>
+      <c r="AA20" t="s">
+        <v>641</v>
+      </c>
     </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>435</v>
       </c>
@@ -3881,7 +4036,7 @@
         <v>438</v>
       </c>
       <c r="E21" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="F21" t="s">
         <v>439</v>
@@ -3946,8 +4101,11 @@
       <c r="Z21" t="s">
         <v>456</v>
       </c>
+      <c r="AA21" t="s">
+        <v>74</v>
+      </c>
     </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>457</v>
       </c>
@@ -3961,7 +4119,7 @@
         <v>460</v>
       </c>
       <c r="E22" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="F22" t="s">
         <v>461</v>
@@ -4026,8 +4184,11 @@
       <c r="Z22" t="s">
         <v>478</v>
       </c>
+      <c r="AA22" t="s">
+        <v>642</v>
+      </c>
     </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>479</v>
       </c>
@@ -4041,7 +4202,7 @@
         <v>482</v>
       </c>
       <c r="E23" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="F23" t="s">
         <v>483</v>
@@ -4106,8 +4267,11 @@
       <c r="Z23" t="s">
         <v>499</v>
       </c>
+      <c r="AA23" t="s">
+        <v>643</v>
+      </c>
     </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>500</v>
       </c>
@@ -4121,7 +4285,7 @@
         <v>503</v>
       </c>
       <c r="E24" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="F24" t="s">
         <v>504</v>
@@ -4178,7 +4342,7 @@
         <v>516</v>
       </c>
       <c r="X24" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="Y24" t="s">
         <v>517</v>
@@ -4186,13 +4350,16 @@
       <c r="Z24" t="s">
         <v>518</v>
       </c>
+      <c r="AA24" t="s">
+        <v>644</v>
+      </c>
     </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>519</v>
       </c>
       <c r="B25" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C25" t="s">
         <v>520</v>
@@ -4201,7 +4368,7 @@
         <v>521</v>
       </c>
       <c r="E25" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F25" t="s">
         <v>522</v>
@@ -4258,7 +4425,7 @@
         <v>535</v>
       </c>
       <c r="X25" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Y25" t="s">
         <v>536</v>
@@ -4266,13 +4433,16 @@
       <c r="Z25" t="s">
         <v>537</v>
       </c>
+      <c r="AA25" t="s">
+        <v>645</v>
+      </c>
     </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>538</v>
       </c>
       <c r="B26" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C26" t="s">
         <v>539</v>
@@ -4281,7 +4451,7 @@
         <v>540</v>
       </c>
       <c r="E26" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="F26" t="s">
         <v>541</v>
@@ -4335,10 +4505,10 @@
         <v>554</v>
       </c>
       <c r="W26" t="s">
+        <v>622</v>
+      </c>
+      <c r="X26" t="s">
         <v>623</v>
-      </c>
-      <c r="X26" t="s">
-        <v>624</v>
       </c>
       <c r="Y26" t="s">
         <v>555</v>
@@ -4346,28 +4516,31 @@
       <c r="Z26" t="s">
         <v>556</v>
       </c>
+      <c r="AA26" t="s">
+        <v>646</v>
+      </c>
     </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>557</v>
       </c>
       <c r="B27" t="s">
+        <v>648</v>
+      </c>
+      <c r="C27" t="s">
         <v>558</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
         <v>559</v>
       </c>
-      <c r="D27" t="s">
+      <c r="E27" t="s">
+        <v>597</v>
+      </c>
+      <c r="F27" t="s">
         <v>560</v>
       </c>
-      <c r="E27" t="s">
-        <v>598</v>
-      </c>
-      <c r="F27" t="s">
+      <c r="G27" t="s">
         <v>561</v>
-      </c>
-      <c r="G27" t="s">
-        <v>562</v>
       </c>
       <c r="H27">
         <v>3851234</v>
@@ -4376,55 +4549,58 @@
         <v>420</v>
       </c>
       <c r="J27" t="s">
+        <v>562</v>
+      </c>
+      <c r="K27" t="s">
         <v>563</v>
       </c>
-      <c r="K27" t="s">
+      <c r="L27" t="s">
         <v>564</v>
       </c>
-      <c r="L27" t="s">
+      <c r="M27" t="s">
         <v>565</v>
       </c>
-      <c r="M27" t="s">
+      <c r="N27" t="s">
         <v>566</v>
-      </c>
-      <c r="N27" t="s">
-        <v>567</v>
       </c>
       <c r="O27">
         <v>1174916</v>
       </c>
       <c r="P27" t="s">
+        <v>567</v>
+      </c>
+      <c r="Q27" t="s">
         <v>568</v>
       </c>
-      <c r="Q27" t="s">
+      <c r="R27" t="s">
         <v>569</v>
       </c>
-      <c r="R27" t="s">
+      <c r="S27" t="s">
         <v>570</v>
       </c>
-      <c r="S27" t="s">
+      <c r="T27" t="s">
         <v>571</v>
       </c>
-      <c r="T27" t="s">
+      <c r="U27" t="s">
         <v>572</v>
       </c>
-      <c r="U27" t="s">
+      <c r="V27" t="s">
         <v>573</v>
       </c>
-      <c r="V27" t="s">
+      <c r="W27" t="s">
         <v>574</v>
       </c>
-      <c r="W27" t="s">
+      <c r="X27" t="s">
+        <v>624</v>
+      </c>
+      <c r="Y27" t="s">
         <v>575</v>
       </c>
-      <c r="X27" t="s">
-        <v>625</v>
-      </c>
-      <c r="Y27" t="s">
+      <c r="Z27" t="s">
         <v>576</v>
       </c>
-      <c r="Z27" t="s">
-        <v>577</v>
+      <c r="AA27" t="s">
+        <v>647</v>
       </c>
     </row>
   </sheetData>
